--- a/data/raw/김포 25년/항공통계상세조회(노선) (2).xlsx
+++ b/data/raw/김포 25년/항공통계상세조회(노선) (2).xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="68">
   <si>
     <t>SEQ</t>
   </si>
@@ -38,13 +38,13 @@
     <t/>
   </si>
   <si>
-    <t>8822</t>
-  </si>
-  <si>
-    <t>1547546</t>
-  </si>
-  <si>
-    <t>13593</t>
+    <t>4412</t>
+  </si>
+  <si>
+    <t>769333</t>
+  </si>
+  <si>
+    <t>6380</t>
   </si>
   <si>
     <t>김포(GMP)</t>
@@ -53,187 +53,169 @@
     <t>간사이(KIX)</t>
   </si>
   <si>
+    <t>168</t>
+  </si>
+  <si>
+    <t>32842</t>
+  </si>
+  <si>
+    <t>388</t>
+  </si>
+  <si>
+    <t>광주(KWJ)</t>
+  </si>
+  <si>
+    <t>50</t>
+  </si>
+  <si>
+    <t>4453</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>김해(PUS)</t>
+  </si>
+  <si>
+    <t>532</t>
+  </si>
+  <si>
+    <t>81017</t>
+  </si>
+  <si>
+    <t>337</t>
+  </si>
+  <si>
+    <t>다싱(PKX)</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>4815</t>
+  </si>
+  <si>
+    <t>72</t>
+  </si>
+  <si>
+    <t>도쿄 하네다(HND)</t>
+  </si>
+  <si>
     <t>336</t>
   </si>
   <si>
-    <t>68009</t>
-  </si>
-  <si>
-    <t>812</t>
-  </si>
-  <si>
-    <t>광주(KWJ)</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>9647</t>
-  </si>
-  <si>
-    <t>32</t>
-  </si>
-  <si>
-    <t>김해(PUS)</t>
-  </si>
-  <si>
-    <t>1059</t>
-  </si>
-  <si>
-    <t>162070</t>
-  </si>
-  <si>
-    <t>685</t>
-  </si>
-  <si>
-    <t>나트랑캄란(CXR)</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>278</t>
+    <t>75621</t>
+  </si>
+  <si>
+    <t>1395</t>
+  </si>
+  <si>
+    <t>북경(PEK)</t>
+  </si>
+  <si>
+    <t>73</t>
+  </si>
+  <si>
+    <t>8936</t>
+  </si>
+  <si>
+    <t>116</t>
+  </si>
+  <si>
+    <t>사천(HIN)</t>
+  </si>
+  <si>
+    <t>52</t>
+  </si>
+  <si>
+    <t>5417</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>쑹산(TSA)</t>
+  </si>
+  <si>
+    <t>56</t>
+  </si>
+  <si>
+    <t>9987</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>여수(RSU)</t>
+  </si>
+  <si>
+    <t>75</t>
+  </si>
+  <si>
+    <t>8490</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>울산(USN)</t>
+  </si>
+  <si>
+    <t>83</t>
+  </si>
+  <si>
+    <t>9235</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>제주(CJU)</t>
+  </si>
+  <si>
+    <t>2780</t>
+  </si>
+  <si>
+    <t>497065</t>
+  </si>
+  <si>
+    <t>3445</t>
+  </si>
+  <si>
+    <t>카오슝(KHH)</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>6593</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>포항 경주(KPO)</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>1538</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>다낭(DAD)</t>
-  </si>
-  <si>
-    <t>275</t>
-  </si>
-  <si>
-    <t>다싱(PKX)</t>
-  </si>
-  <si>
-    <t>56</t>
-  </si>
-  <si>
-    <t>9614</t>
-  </si>
-  <si>
-    <t>144</t>
-  </si>
-  <si>
-    <t>도쿄 하네다(HND)</t>
-  </si>
-  <si>
-    <t>670</t>
-  </si>
-  <si>
-    <t>155280</t>
-  </si>
-  <si>
-    <t>2416</t>
-  </si>
-  <si>
-    <t>북경(PEK)</t>
-  </si>
-  <si>
-    <t>146</t>
-  </si>
-  <si>
-    <t>17846</t>
-  </si>
-  <si>
-    <t>227</t>
-  </si>
-  <si>
-    <t>사천(HIN)</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>11394</t>
-  </si>
-  <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>쑹산(TSA)</t>
+    <t>홍차오(SHA)</t>
   </si>
   <si>
     <t>112</t>
   </si>
   <si>
-    <t>19366</t>
-  </si>
-  <si>
-    <t>250</t>
-  </si>
-  <si>
-    <t>여수(RSU)</t>
-  </si>
-  <si>
-    <t>149</t>
-  </si>
-  <si>
-    <t>16778</t>
-  </si>
-  <si>
-    <t>52</t>
-  </si>
-  <si>
-    <t>울산(USN)</t>
-  </si>
-  <si>
-    <t>166</t>
-  </si>
-  <si>
-    <t>19043</t>
-  </si>
-  <si>
-    <t>64</t>
-  </si>
-  <si>
-    <t>제주(CJU)</t>
-  </si>
-  <si>
-    <t>5561</t>
-  </si>
-  <si>
-    <t>998675</t>
-  </si>
-  <si>
-    <t>7872</t>
-  </si>
-  <si>
-    <t>카오슝(KHH)</t>
-  </si>
-  <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>12471</t>
-  </si>
-  <si>
-    <t>161</t>
-  </si>
-  <si>
-    <t>포항 경주(KPO)</t>
-  </si>
-  <si>
-    <t>54</t>
-  </si>
-  <si>
-    <t>3140</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>홍차오(SHA)</t>
-  </si>
-  <si>
-    <t>224</t>
-  </si>
-  <si>
-    <t>43660</t>
-  </si>
-  <si>
-    <t>840</t>
+    <t>23324</t>
+  </si>
+  <si>
+    <t>315</t>
   </si>
 </sst>
 </file>
@@ -284,7 +266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="30"/>
   <sheetData>
     <row r="1">
@@ -418,13 +400,13 @@
         <v>28</v>
       </c>
       <c r="D7" t="s" s="0">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E7" t="s" s="0">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F7" t="s" s="0">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -435,16 +417,16 @@
         <v>11</v>
       </c>
       <c r="C8" t="s" s="0">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D8" t="s" s="0">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s" s="0">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F8" t="s" s="0">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
@@ -455,16 +437,16 @@
         <v>11</v>
       </c>
       <c r="C9" t="s" s="0">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s" s="0">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E9" t="s" s="0">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F9" t="s" s="0">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="10">
@@ -475,16 +457,16 @@
         <v>11</v>
       </c>
       <c r="C10" t="s" s="0">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10" t="s" s="0">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E10" t="s" s="0">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F10" t="s" s="0">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
@@ -495,16 +477,16 @@
         <v>11</v>
       </c>
       <c r="C11" t="s" s="0">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D11" t="s" s="0">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E11" t="s" s="0">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F11" t="s" s="0">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
@@ -515,16 +497,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="s" s="0">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s" s="0">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E12" t="s" s="0">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F12" t="s" s="0">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="13">
@@ -535,16 +517,16 @@
         <v>11</v>
       </c>
       <c r="C13" t="s" s="0">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D13" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E13" t="s" s="0">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F13" t="s" s="0">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14">
@@ -555,16 +537,16 @@
         <v>11</v>
       </c>
       <c r="C14" t="s" s="0">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D14" t="s" s="0">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E14" t="s" s="0">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="F14" t="s" s="0">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15">
@@ -575,16 +557,16 @@
         <v>11</v>
       </c>
       <c r="C15" t="s" s="0">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D15" t="s" s="0">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E15" t="s" s="0">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="F15" t="s" s="0">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="16">
@@ -595,56 +577,16 @@
         <v>11</v>
       </c>
       <c r="C16" t="s" s="0">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D16" t="s" s="0">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F16" t="s" s="0">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n" s="0">
-        <v>15.0</v>
-      </c>
-      <c r="B17" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C17" t="s" s="0">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s" s="0">
         <v>67</v>
-      </c>
-      <c r="E17" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="F17" t="s" s="0">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n" s="0">
-        <v>16.0</v>
-      </c>
-      <c r="B18" t="s" s="0">
-        <v>11</v>
-      </c>
-      <c r="C18" t="s" s="0">
-        <v>70</v>
-      </c>
-      <c r="D18" t="s" s="0">
-        <v>71</v>
-      </c>
-      <c r="E18" t="s" s="0">
-        <v>72</v>
-      </c>
-      <c r="F18" t="s" s="0">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
